--- a/00_output/12_loadshape.xlsx
+++ b/00_output/12_loadshape.xlsx
@@ -1,137 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/00_output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_68A0CEC4DD4E92CEEB3B98154B8D76B9ACFCDAFC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06034D2F-0F99-4864-A902-B98D4CDBED29}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="loadshape" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="loadshape" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>unique_measure_name</t>
-  </si>
-  <si>
-    <t>summer_on-peak</t>
-  </si>
-  <si>
-    <t>summer_off-peak</t>
-  </si>
-  <si>
-    <t>winter_on-peak</t>
-  </si>
-  <si>
-    <t>winter_off-peak</t>
-  </si>
-  <si>
-    <t>shoulder_on-peak</t>
-  </si>
-  <si>
-    <t>shoulder_off-peak</t>
-  </si>
-  <si>
-    <t>summer_gener._capacity</t>
-  </si>
-  <si>
-    <t>winter_gener_capacity</t>
-  </si>
-  <si>
-    <t>summer_td</t>
-  </si>
-  <si>
-    <t>winter_td</t>
-  </si>
-  <si>
-    <t>furnace_efficient_oil_residential</t>
-  </si>
-  <si>
-    <t>furnace_baseline_oil_residential</t>
-  </si>
-  <si>
-    <t>furnace_existing_oil_residential</t>
-  </si>
-  <si>
-    <t>furnace_efficient_natural_gas_residential</t>
-  </si>
-  <si>
-    <t>furnace_baseline_natural_gas_residential</t>
-  </si>
-  <si>
-    <t>furnace_existing_natural_gas_residential</t>
-  </si>
-  <si>
-    <t>central_ac_efficient_electric_residential</t>
-  </si>
-  <si>
-    <t>central_ac_baseline_electric_residential</t>
-  </si>
-  <si>
-    <t>central_ac_existing_electric_residential</t>
-  </si>
-  <si>
-    <t>room_ac_efficient_electric_residential</t>
-  </si>
-  <si>
-    <t>room_ac_baseline_electric_residential</t>
-  </si>
-  <si>
-    <t>room_ac_existing_electric_residential</t>
-  </si>
-  <si>
-    <t>fridge_efficient_electric_residential</t>
-  </si>
-  <si>
-    <t>fridge_baseline_electric_residential</t>
-  </si>
-  <si>
-    <t>fridge_top10_electric_residential</t>
-  </si>
-  <si>
-    <t>fridge_existing_electric_residential</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -150,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -452,126 +408,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>26</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>unique_measure_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>summer_on-peak</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>summer_off-peak</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>winter_on-peak</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>winter_off-peak</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>shoulder_on-peak</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shoulder_off-peak</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>summer_gener_capacity</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>winter_gener_capacity</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>summer_td</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>winter_td</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>furnace_efficient_oil_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>furnace_baseline_oil_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>furnace_existing_oil_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>furnace_efficient_natural_gas_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>furnace_baseline_natural_gas_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>furnace_existing_natural_gas_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>fridge_efficient_electric_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>fridge_baseline_electric_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>fridge_top10_electric_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>fridge_existing_electric_residential</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/00_output/12_loadshape.xlsx
+++ b/00_output/12_loadshape.xlsx
@@ -476,70 +476,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>furnace_efficient_oil_residential</t>
+          <t>furnace_oil_efficient_residential</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_baseline_oil_residential</t>
+          <t>furnace_oil_baseline_residential</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_existing_oil_residential</t>
+          <t>furnace_oil_existing_residential</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_efficient_natural_gas_residential</t>
+          <t>furnace_natural_gas_efficient_residential</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_baseline_natural_gas_residential</t>
+          <t>furnace_natural_gas_baseline_residential</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_existing_natural_gas_residential</t>
+          <t>furnace_natural_gas_existing_residential</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fridge_efficient_electric_residential</t>
+          <t>fridge_electric_efficient_residential</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fridge_baseline_electric_residential</t>
+          <t>fridge_electric_baseline_residential</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fridge_top10_electric_residential</t>
+          <t>fridge_electric_top10_residential</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fridge_existing_electric_residential</t>
+          <t>fridge_electric_existing_residential</t>
         </is>
       </c>
     </row>

--- a/00_output/12_loadshape.xlsx
+++ b/00_output/12_loadshape.xlsx
@@ -518,28 +518,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fridge_electric_efficient_residential</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fridge_electric_baseline_residential</t>
+          <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fridge_electric_top10_residential</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fridge_electric_existing_residential</t>
+          <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
     </row>

--- a/00_output/12_loadshape.xlsx
+++ b/00_output/12_loadshape.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,68 +476,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>

--- a/00_output/12_loadshape.xlsx
+++ b/00_output/12_loadshape.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -42,12 +57,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,177 +458,351 @@
   </sheetPr>
   <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>unique_measure_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>summer_on-peak</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>summer_off-peak</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>winter_on-peak</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>winter_off-peak</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>shoulder_on-peak</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>shoulder_off-peak</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>summer_gener_capacity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>winter_gener_capacity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>summer_td</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>winter_td</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>furnace_oil_efficient_residential_1</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential_1a</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>furnace_oil_baseline_residential_1</t>
-        </is>
-      </c>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential_1a</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>furnace_oil_existing_residential_1</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential_1a</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>furnace_oil_efficient_residential_2</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential_3b</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>furnace_oil_baseline_residential_2</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential_3b</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>furnace_oil_existing_residential_2</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential_3b</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_efficient_residential_1</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_1a</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_baseline_residential_1</t>
-        </is>
-      </c>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_1a</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_existing_residential_1</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_1a</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_efficient_residential_2</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_3b</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_baseline_residential_2</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_3b</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_existing_residential_2</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_3b</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/00_output/12_loadshape.xlsx
+++ b/00_output/12_loadshape.xlsx
@@ -459,7 +459,7 @@
   <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -468,8 +468,8 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
